--- a/7 Future comparisons/Bonaire/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/7 Future comparisons/Bonaire/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.950499243969539</v>
+        <v>2.084877328575738</v>
       </c>
       <c r="C3" t="n">
-        <v>2.823583722270888</v>
+        <v>3.00949190265318</v>
       </c>
       <c r="D3" t="n">
-        <v>36.96959475900579</v>
+        <v>38.35012273744155</v>
       </c>
       <c r="E3" t="n">
-        <v>41.74367772524622</v>
+        <v>43.44449196867047</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.863239332935936</v>
+        <v>2.090131755433503</v>
       </c>
       <c r="C4" t="n">
-        <v>2.868018838324377</v>
+        <v>3.20923421482358</v>
       </c>
       <c r="D4" t="n">
-        <v>36.51920818220552</v>
+        <v>39.15039319165349</v>
       </c>
       <c r="E4" t="n">
-        <v>41.25046635346584</v>
+        <v>44.44975916191057</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.811854658095658</v>
+        <v>2.118635819065871</v>
       </c>
       <c r="C5" t="n">
-        <v>2.937850552527453</v>
+        <v>3.427109355055703</v>
       </c>
       <c r="D5" t="n">
-        <v>35.81268362936727</v>
+        <v>39.61679168741046</v>
       </c>
       <c r="E5" t="n">
-        <v>40.56238883999038</v>
+        <v>45.16253686153204</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.762580740819511</v>
+        <v>2.135137853454967</v>
       </c>
       <c r="C6" t="n">
-        <v>3.13191262122592</v>
+        <v>3.756460351953768</v>
       </c>
       <c r="D6" t="n">
-        <v>35.86130959315862</v>
+        <v>40.70232199871385</v>
       </c>
       <c r="E6" t="n">
-        <v>40.75580295520405</v>
+        <v>46.59392020412258</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.8675998986740339</v>
+        <v>1.051008996614121</v>
       </c>
       <c r="C7" t="n">
-        <v>2.173628687110608</v>
+        <v>2.567214465581448</v>
       </c>
       <c r="D7" t="n">
-        <v>26.24516936987745</v>
+        <v>30.02169184824038</v>
       </c>
       <c r="E7" t="n">
-        <v>29.28639795566209</v>
+        <v>33.63991531043595</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9199859561726437</v>
+        <v>1.137171246870649</v>
       </c>
       <c r="C8" t="n">
-        <v>2.627235396380804</v>
+        <v>3.095017164673054</v>
       </c>
       <c r="D8" t="n">
-        <v>26.99385998661311</v>
+        <v>31.42037028691053</v>
       </c>
       <c r="E8" t="n">
-        <v>30.54108133916656</v>
+        <v>35.65255869845423</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5966375323019142</v>
+        <v>0.7555333982342604</v>
       </c>
       <c r="C9" t="n">
-        <v>2.267856831764217</v>
+        <v>2.590203872976614</v>
       </c>
       <c r="D9" t="n">
-        <v>21.96382653651936</v>
+        <v>25.78846033786184</v>
       </c>
       <c r="E9" t="n">
-        <v>24.8283209005855</v>
+        <v>29.13419760907271</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5685595479604554</v>
+        <v>0.7188454865265571</v>
       </c>
       <c r="C10" t="n">
-        <v>2.653693497010256</v>
+        <v>2.925568888747325</v>
       </c>
       <c r="D10" t="n">
-        <v>20.96491788240232</v>
+        <v>24.42028691974644</v>
       </c>
       <c r="E10" t="n">
-        <v>24.18717092737303</v>
+        <v>28.06470129502032</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6169498923027806</v>
+        <v>0.7827179921648545</v>
       </c>
       <c r="C11" t="n">
-        <v>3.447829214975501</v>
+        <v>3.736040888511238</v>
       </c>
       <c r="D11" t="n">
-        <v>21.74611416562559</v>
+        <v>25.44921741865934</v>
       </c>
       <c r="E11" t="n">
-        <v>25.81089327290388</v>
+        <v>29.96797629933544</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.6806751357854411</v>
+        <v>0.861503245430661</v>
       </c>
       <c r="C12" t="n">
-        <v>4.504690436074235</v>
+        <v>4.828608273613427</v>
       </c>
       <c r="D12" t="n">
-        <v>22.64182150107221</v>
+        <v>26.6889880545363</v>
       </c>
       <c r="E12" t="n">
-        <v>27.82718707293188</v>
+        <v>32.37909957358039</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.736124246121301</v>
+        <v>0.9376083274638739</v>
       </c>
       <c r="C13" t="n">
-        <v>5.770820997810218</v>
+        <v>6.106166399243718</v>
       </c>
       <c r="D13" t="n">
-        <v>24.23505076290914</v>
+        <v>28.63727619109114</v>
       </c>
       <c r="E13" t="n">
-        <v>30.74199600684066</v>
+        <v>35.68105091779874</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.7772791098833273</v>
+        <v>1.003552320758132</v>
       </c>
       <c r="C14" t="n">
-        <v>7.239682460473169</v>
+        <v>7.565157943325771</v>
       </c>
       <c r="D14" t="n">
-        <v>25.33818175330903</v>
+        <v>30.07191392878405</v>
       </c>
       <c r="E14" t="n">
-        <v>33.35514332366552</v>
+        <v>38.64062419286795</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8038942901454582</v>
+        <v>1.05505480532292</v>
       </c>
       <c r="C15" t="n">
-        <v>8.858456797574608</v>
+        <v>9.17936276004114</v>
       </c>
       <c r="D15" t="n">
-        <v>27.01268009010352</v>
+        <v>32.08655839266893</v>
       </c>
       <c r="E15" t="n">
-        <v>36.67503117782358</v>
+        <v>42.32097595803299</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8178351075457631</v>
+        <v>1.086784891124177</v>
       </c>
       <c r="C16" t="n">
-        <v>10.71017041246269</v>
+        <v>11.00129232172046</v>
       </c>
       <c r="D16" t="n">
-        <v>27.80953524920953</v>
+        <v>33.24616932849413</v>
       </c>
       <c r="E16" t="n">
-        <v>39.33754076921798</v>
+        <v>45.33424654133877</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8164213908516474</v>
+        <v>1.098182981970482</v>
       </c>
       <c r="C17" t="n">
-        <v>12.62187862955729</v>
+        <v>12.85162319590652</v>
       </c>
       <c r="D17" t="n">
-        <v>29.22799378473645</v>
+        <v>34.96068370171372</v>
       </c>
       <c r="E17" t="n">
-        <v>42.66629380514539</v>
+        <v>48.91048987959072</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8039531950077131</v>
+        <v>1.100077755039678</v>
       </c>
       <c r="C18" t="n">
-        <v>14.59609472298128</v>
+        <v>14.73904127640618</v>
       </c>
       <c r="D18" t="n">
-        <v>30.07646923813175</v>
+        <v>36.1044786820235</v>
       </c>
       <c r="E18" t="n">
-        <v>45.47651715612075</v>
+        <v>51.94359771346937</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7787222790085698</v>
+        <v>1.093490227944182</v>
       </c>
       <c r="C19" t="n">
-        <v>16.58119839844538</v>
+        <v>16.62428395044324</v>
       </c>
       <c r="D19" t="n">
-        <v>30.98846376799183</v>
+        <v>37.30188690446221</v>
       </c>
       <c r="E19" t="n">
-        <v>48.34838444544578</v>
+        <v>55.01966108284964</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.7499276188430108</v>
+        <v>1.081542358383499</v>
       </c>
       <c r="C20" t="n">
-        <v>18.56624316904722</v>
+        <v>18.49016837103256</v>
       </c>
       <c r="D20" t="n">
-        <v>31.34914805705506</v>
+        <v>37.92490399757725</v>
       </c>
       <c r="E20" t="n">
-        <v>50.66531884494529</v>
+        <v>57.4966147269933</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.7163616648348125</v>
+        <v>1.057892056188193</v>
       </c>
       <c r="C21" t="n">
-        <v>20.56037892339038</v>
+        <v>20.34280739604991</v>
       </c>
       <c r="D21" t="n">
-        <v>31.74889608727028</v>
+        <v>38.60277421415714</v>
       </c>
       <c r="E21" t="n">
-        <v>53.02563667549548</v>
+        <v>60.00347366639524</v>
       </c>
     </row>
     <row r="22">
@@ -800,16 +800,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>0.6786134656065227</v>
+        <v>1.0288814115277</v>
       </c>
       <c r="C22" t="n">
-        <v>22.42575846632157</v>
+        <v>22.04939112331197</v>
       </c>
       <c r="D22" t="n">
-        <v>32.22986410505784</v>
+        <v>39.24779921157278</v>
       </c>
       <c r="E22" t="n">
-        <v>55.33423603698593</v>
+        <v>62.32607174641245</v>
       </c>
     </row>
     <row r="23">
@@ -817,16 +817,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.6388134136763569</v>
+        <v>0.988580668268368</v>
       </c>
       <c r="C23" t="n">
-        <v>24.24326799119369</v>
+        <v>23.71567318749798</v>
       </c>
       <c r="D23" t="n">
-        <v>32.36115322554676</v>
+        <v>39.63233996984921</v>
       </c>
       <c r="E23" t="n">
-        <v>57.24323463041681</v>
+        <v>64.33659382561555</v>
       </c>
     </row>
     <row r="24">
@@ -834,16 +834,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.599572957937612</v>
+        <v>0.9444609264395165</v>
       </c>
       <c r="C24" t="n">
-        <v>26.15837305534498</v>
+        <v>25.38179066666742</v>
       </c>
       <c r="D24" t="n">
-        <v>32.75720006691697</v>
+        <v>40.19793131397311</v>
       </c>
       <c r="E24" t="n">
-        <v>59.51514608019956</v>
+        <v>66.52418290708005</v>
       </c>
     </row>
     <row r="25">
@@ -851,16 +851,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5600379778875929</v>
+        <v>0.9008222409857457</v>
       </c>
       <c r="C25" t="n">
-        <v>27.87526325800886</v>
+        <v>26.87889905134248</v>
       </c>
       <c r="D25" t="n">
-        <v>32.45876839978002</v>
+        <v>40.17203613530481</v>
       </c>
       <c r="E25" t="n">
-        <v>60.89406963567647</v>
+        <v>67.95175742763304</v>
       </c>
     </row>
     <row r="26">
@@ -868,16 +868,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5191481860057133</v>
+        <v>0.8542579473733196</v>
       </c>
       <c r="C26" t="n">
-        <v>29.62720185371433</v>
+        <v>28.37677962135181</v>
       </c>
       <c r="D26" t="n">
-        <v>32.62070768359553</v>
+        <v>40.49940972476295</v>
       </c>
       <c r="E26" t="n">
-        <v>62.76705772331557</v>
+        <v>69.73044729348808</v>
       </c>
     </row>
     <row r="27">
@@ -885,16 +885,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.4803495167338793</v>
+        <v>0.8054356340411256</v>
       </c>
       <c r="C27" t="n">
-        <v>31.32954255540125</v>
+        <v>29.81365803275543</v>
       </c>
       <c r="D27" t="n">
-        <v>32.47265031231807</v>
+        <v>40.5226771453536</v>
       </c>
       <c r="E27" t="n">
-        <v>64.28254238445321</v>
+        <v>71.14177081215016</v>
       </c>
     </row>
     <row r="28">
@@ -902,16 +902,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.44395612933745</v>
+        <v>0.7575950684131786</v>
       </c>
       <c r="C28" t="n">
-        <v>32.80504063254491</v>
+        <v>31.03535108838504</v>
       </c>
       <c r="D28" t="n">
-        <v>32.08396657872972</v>
+        <v>40.33711701177391</v>
       </c>
       <c r="E28" t="n">
-        <v>65.33296334061207</v>
+        <v>72.13006316857214</v>
       </c>
     </row>
   </sheetData>
